--- a/src/excel-data/national.xlsx
+++ b/src/excel-data/national.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/Cao Yuxuan/テストweb/findmyrailpass.net/src/excel-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDF6D04-F28F-CF45-918E-C407D54CD924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D315E259-E31C-6949-BBB1-DD1552DE410C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全国周游券" sheetId="1" r:id="rId1"/>
@@ -121,12 +121,6 @@
     <t>新干线; 特急电车; 急行电车; 普通电车; JR巴士</t>
   </si>
   <si>
-    <t>JR官方; https://japanrailpass.net/cn/purchase/price/</t>
-  </si>
-  <si>
-    <t>官方购买; https://japanrailpass.net/cn/purchase/online/; type:official</t>
-  </si>
-  <si>
     <t>national</t>
   </si>
   <si>
@@ -221,6 +215,14 @@
   </si>
   <si>
     <t>ticket_note</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://japanrailpass.net/cn/purchase/price/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://japanrailpass.net/cn/purchase/online/; type:official</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -252,12 +254,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -273,9 +281,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -623,6 +633,9 @@
     <col min="10" max="10" width="22.83203125" customWidth="1"/>
     <col min="11" max="11" width="34.33203125" customWidth="1"/>
     <col min="12" max="13" width="16.5" customWidth="1"/>
+    <col min="22" max="22" width="55.1640625" customWidth="1"/>
+    <col min="23" max="23" width="44" customWidth="1"/>
+    <col min="24" max="24" width="69.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -651,7 +664,7 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -660,10 +673,10 @@
         <v>9</v>
       </c>
       <c r="L1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N1" t="s">
         <v>22</v>
@@ -708,420 +721,420 @@
         <v>23</v>
       </c>
       <c r="AB1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" s="2" customFormat="1">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2">
+        <v>50000</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="2">
+        <v>25000</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="2">
+        <v>7</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="X2" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="2" spans="1:28">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2">
+      <c r="Y2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>5</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" s="2" customFormat="1">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="2">
+        <v>80000</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="2">
+        <v>40000</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="2">
+        <v>14</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>5</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" s="2" customFormat="1">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="2">
         <v>50000</v>
       </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2">
-        <v>25000</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2">
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" s="2">
+        <v>21</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" s="2" customFormat="1">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="2">
+        <v>70000</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="2">
+        <v>35000</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" s="2">
         <v>7</v>
       </c>
-      <c r="P2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="P5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="T2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="T5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="X2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z2">
+      <c r="Z5" s="2">
         <v>5</v>
       </c>
-      <c r="AA2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3">
-        <v>80000</v>
-      </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3">
-        <v>40000</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" t="s">
-        <v>41</v>
-      </c>
-      <c r="O3">
+      <c r="AA5" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" s="2" customFormat="1">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="2">
+        <v>110000</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="2">
+        <v>55000</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="2">
         <v>14</v>
       </c>
-      <c r="P3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>27</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="P6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="T3" t="s">
-        <v>40</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="T6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="X3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z3">
-        <v>5</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4">
-        <v>100000</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4">
-        <v>50000</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" t="s">
-        <v>46</v>
-      </c>
-      <c r="O4">
+      <c r="Z6" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" s="2" customFormat="1">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="2">
+        <v>140000</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2">
+        <v>70000</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" s="2">
         <v>21</v>
       </c>
-      <c r="P4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>27</v>
-      </c>
-      <c r="R4" t="s">
+      <c r="P7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="S4" t="s">
+      <c r="S7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="T4" t="s">
-        <v>45</v>
-      </c>
-      <c r="U4" t="s">
+      <c r="T7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="U7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="X7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="X4" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z4">
-        <v>5</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28">
-      <c r="A5">
+      <c r="Z7" s="2">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5">
-        <v>70000</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5">
-        <v>35000</v>
-      </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O5">
-        <v>7</v>
-      </c>
-      <c r="P5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>27</v>
-      </c>
-      <c r="R5" t="s">
-        <v>28</v>
-      </c>
-      <c r="S5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T5" t="s">
-        <v>50</v>
-      </c>
-      <c r="U5" t="s">
-        <v>31</v>
-      </c>
-      <c r="V5" t="s">
-        <v>32</v>
-      </c>
-      <c r="W5" t="s">
-        <v>33</v>
-      </c>
-      <c r="X5" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z5">
-        <v>5</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6">
-        <v>110000</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6">
-        <v>55000</v>
-      </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" t="s">
-        <v>56</v>
-      </c>
-      <c r="O6">
-        <v>14</v>
-      </c>
-      <c r="P6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>27</v>
-      </c>
-      <c r="R6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S6" t="s">
-        <v>29</v>
-      </c>
-      <c r="T6" t="s">
-        <v>55</v>
-      </c>
-      <c r="U6" t="s">
-        <v>31</v>
-      </c>
-      <c r="V6" t="s">
-        <v>32</v>
-      </c>
-      <c r="W6" t="s">
-        <v>33</v>
-      </c>
-      <c r="X6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z6">
-        <v>4</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7">
-        <v>140000</v>
-      </c>
-      <c r="F7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7">
-        <v>70000</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" t="s">
-        <v>61</v>
-      </c>
-      <c r="O7">
-        <v>21</v>
-      </c>
-      <c r="P7" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>27</v>
-      </c>
-      <c r="R7" t="s">
-        <v>28</v>
-      </c>
-      <c r="S7" t="s">
-        <v>29</v>
-      </c>
-      <c r="T7" t="s">
-        <v>60</v>
-      </c>
-      <c r="U7" t="s">
-        <v>31</v>
-      </c>
-      <c r="V7" t="s">
-        <v>32</v>
-      </c>
-      <c r="W7" t="s">
-        <v>33</v>
-      </c>
-      <c r="X7" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z7">
-        <v>4</v>
-      </c>
-      <c r="AA7" t="s">
+      <c r="AA7" s="2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1462,9 +1475,13 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="W2" r:id="rId1" xr:uid="{791958D3-79C0-6742-AB32-BA49B53F442D}"/>
+    <hyperlink ref="W3:W7" r:id="rId2" display="https://japanrailpass.net/cn/purchase/price/" xr:uid="{8B4FB220-3CD4-F643-AAFF-FAD8A50650B8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="O1:AA1 A1:E7 F1:G7 H1:H7 P4:AA4 P2:AA2 P3:AA3 P7:AA7 P5:AA5 P6:AA6" numberStoredAsText="1"/>
+    <ignoredError sqref="O1:AA1 A1:E7 F1:G7 H1:H7 P4:V4 P2:V2 P3:V3 P7:V7 P5:V5 P6:V6 Y2:AA2 Y4:AA4 Y3:AA3 Y7:AA7 Y5:AA5 Y6:AA6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>